--- a/cp-upgrade-mhd/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
+++ b/cp-upgrade-mhd/ig/StructureDefinition-pdsm-comprehensive-document-reference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4211" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4211" uniqueCount="766">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-05T15:39:30+00:00</t>
+    <t>2026-05-05T15:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -240,6 +240,9 @@
     <t>Mapping: Spécification métier vers le profil PDSm_ComprehensiveDocumentReference</t>
   </si>
   <si>
+    <t>Mapping: XDS and MHD Mapping</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -259,9 +262,6 @@
   </si>
   <si>
     <t>Mapping: XDS metadata equivalent</t>
-  </si>
-  <si>
-    <t>Mapping: XDS and MHD Mapping</t>
   </si>
   <si>
     <t/>
@@ -287,12 +287,15 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}iti-mhd-repl:a DocumetReference replacements needs to relate to a superseded DocumentReference {relatesTo.empty() or (relatesTo.code='replaces' implies relatesTo.target.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Fiche</t>
   </si>
   <si>
+    <t>XDS DocumentEntry: Used in the context of the IHE MHD ImplementationGuide</t>
+  </si>
+  <si>
     <t>Event</t>
   </si>
   <si>
@@ -303,9 +306,6 @@
   </si>
   <si>
     <t>when describing a CDA</t>
-  </si>
-  <si>
-    <t>XDS DocumentEntry</t>
   </si>
   <si>
     <t>DocumentReference.id</t>
@@ -469,7 +469,7 @@
     <t>DocumentReference.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -510,7 +510,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -534,7 +534,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -577,7 +577,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -686,7 +686,7 @@
     <t>Représente l’identifiant unique global affecté au document par son créateur. Il est utilisable comme référence externe dans d’autres documents.</t>
   </si>
   <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+    <t>Document identifier as assigned by the source of the document. This identifier is specific to this version of the document. This unique identifier may be used elsewhere to identify this version of the document.</t>
   </si>
   <si>
     <t>CDA Document Id extension and root.</t>
@@ -698,13 +698,25 @@
     <t>idUnique : [0..1] Identifiant</t>
   </si>
   <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
     <t>DocumentEntry.uniqueId</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>Composition.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>TXA-12</t>
   </si>
   <si>
     <t>DocumentReference.identifier</t>
@@ -727,19 +739,13 @@
     <t>idFiche : [0..*] Identifiant</t>
   </si>
   <si>
-    <t>Event.identifier</t>
+    <t>DocumentEntry.entryUUID</t>
   </si>
   <si>
     <t>.id / .setId</t>
   </si>
   <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
     <t>TXA-16?</t>
-  </si>
-  <si>
-    <t>DocumentEntry.entryUUID</t>
   </si>
   <si>
     <t>DocumentReference.identifier:entryUUID</t>
@@ -752,9 +758,6 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
     <t>DocumentReference.status</t>
   </si>
   <si>
@@ -774,6 +777,9 @@
     <t>https://profiles.ihe.net/ITI/MHD/ValueSet/DocumentReferenceStats</t>
   </si>
   <si>
+    <t>DocumentEntry.availabilityStatus</t>
+  </si>
+  <si>
     <t>Event.status</t>
   </si>
   <si>
@@ -784,9 +790,6 @@
   </si>
   <si>
     <t>TXA-19</t>
-  </si>
-  <si>
-    <t>DocumentEntry.availabilityStatus</t>
   </si>
   <si>
     <t>DocumentReference.docStatus</t>
@@ -847,6 +850,9 @@
     <t>typeDocument : [0..1] Code</t>
   </si>
   <si>
+    <t>DocumentEntry.typeCode</t>
+  </si>
+  <si>
     <t>Event.code</t>
   </si>
   <si>
@@ -867,9 +873,6 @@
   </si>
   <si>
     <t>DocumentEntry.type</t>
-  </si>
-  <si>
-    <t>DocumentEntry.typeCode</t>
   </si>
   <si>
     <t>DocumentReference.category</t>
@@ -902,6 +905,9 @@
     <t>classeDocument : [0..1] Code</t>
   </si>
   <si>
+    <t>DocumentEntry.classCode</t>
+  </si>
+  <si>
     <t>Composition.class</t>
   </si>
   <si>
@@ -912,9 +918,6 @@
   </si>
   <si>
     <t>DocumentEntry.class</t>
-  </si>
-  <si>
-    <t>DocumentEntry.classCode</t>
   </si>
   <si>
     <t>DocumentReference.subject</t>
@@ -933,6 +936,9 @@
     <t>idPatient : [0..1] Identifiant</t>
   </si>
   <si>
+    <t>DocumentEntry.patientId</t>
+  </si>
+  <si>
     <t>Event.subject</t>
   </si>
   <si>
@@ -949,9 +955,6 @@
   </si>
   <si>
     <t>PID-3 (No standard way to define a Practitioner or Group subject in HL7 v2 MDM message)</t>
-  </si>
-  <si>
-    <t>DocumentEntry.patientId</t>
   </si>
   <si>
     <t>DocumentReference.date</t>
@@ -1001,6 +1004,9 @@
     <t>auteur : [1..*] Identifiant</t>
   </si>
   <si>
+    <t>DocumentEntry.author</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1014,9 +1020,6 @@
   </si>
   <si>
     <t>TXA-9 (No standard way to indicate a Device in HL7 v2 MDM message)</t>
-  </si>
-  <si>
-    <t>DocumentEntry.author</t>
   </si>
   <si>
     <t>DocumentReference.authenticator</t>
@@ -1038,6 +1041,9 @@
     <t>authentificateur : [1..1] Identifiant</t>
   </si>
   <si>
+    <t>DocumentEntry.legalAuthenticator</t>
+  </si>
+  <si>
     <t>Composition.attester</t>
   </si>
   <si>
@@ -1053,13 +1059,10 @@
     <t>TXA-10</t>
   </si>
   <si>
-    <t>DocumentEntry.legalAuthenticator</t>
-  </si>
-  <si>
     <t>DocumentReference.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1072,13 +1075,13 @@
     <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
   </si>
   <si>
+    <t>not mapped</t>
+  </si>
+  <si>
     <t>Composition.custodian</t>
   </si>
   <si>
     <t>.participation[typeCode="RCV"].role[classCode="CUST"].scoper[classCode="ORG" and determinerCode="INST"]</t>
-  </si>
-  <si>
-    <t>not mapped</t>
   </si>
   <si>
     <t>DocumentReference.relatesTo</t>
@@ -1101,13 +1104,13 @@
 constr-cdr-rempl:Elément requis lorsque le flux envoyé correspond au remplacement d'un document {null}constr-bind-relatesTo:Cardinalité contrainte à [1..1] lorsque le flux envoyé correspond au remplacement d’un document. {null}</t>
   </si>
   <si>
+    <t>DocumentEntry Associations</t>
+  </si>
+  <si>
     <t>Composition.relatesTo</t>
   </si>
   <si>
     <t>.outboundRelationship</t>
-  </si>
-  <si>
-    <t>DocumentEntry Associations</t>
   </si>
   <si>
     <t>DocumentReference.relatesTo.id</t>
@@ -1157,6 +1160,9 @@
     <t>association : [0..*] Code</t>
   </si>
   <si>
+    <t>DocumentEntry Associations.type</t>
+  </si>
+  <si>
     <t>Composition.relatesTo.code</t>
   </si>
   <si>
@@ -1166,13 +1172,10 @@
     <t>DocumentEntry Associations type</t>
   </si>
   <si>
-    <t>DocumentEntry Associations.type</t>
-  </si>
-  <si>
     <t>DocumentReference.relatesTo.target</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -1189,6 +1192,9 @@
     <t>idFicheAssociation : [0..*] Identifiant</t>
   </si>
   <si>
+    <t>DocumentEntry Associations.reference</t>
+  </si>
+  <si>
     <t>Composition.relatesTo.target</t>
   </si>
   <si>
@@ -1198,9 +1204,6 @@
     <t>DocumentEntry Associations reference</t>
   </si>
   <si>
-    <t>DocumentEntry Associations.reference</t>
-  </si>
-  <si>
     <t>DocumentReference.description</t>
   </si>
   <si>
@@ -1219,13 +1222,13 @@
     <t>commentaire : [0..1] Texte</t>
   </si>
   <si>
+    <t>DocumentEntry.comments</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode="SUBJ"].target.text</t>
   </si>
   <si>
     <t>TXA-25</t>
-  </si>
-  <si>
-    <t>DocumentEntry.comments</t>
   </si>
   <si>
     <t>DocumentReference.securityLabel</t>
@@ -1251,6 +1254,9 @@
     <t>niveauConfidentialite : [0..*] code</t>
   </si>
   <si>
+    <t>DocumentEntry.confidentialityCode</t>
+  </si>
+  <si>
     <t>Composition.confidentiality, Composition.meta.security</t>
   </si>
   <si>
@@ -1261,9 +1267,6 @@
   </si>
   <si>
     <t>TXA-18</t>
-  </si>
-  <si>
-    <t>DocumentEntry.confidentialityCode</t>
   </si>
   <si>
     <t>DocumentReference.content</t>
@@ -1347,15 +1350,15 @@
     <t>Attachment.contentType</t>
   </si>
   <si>
+    <t>DocumentEntry.mimeType</t>
+  </si>
+  <si>
     <t>./mediaType, ./charset</t>
   </si>
   <si>
     <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
   </si>
   <si>
-    <t>DocumentEntry.mimeType</t>
-  </si>
-  <si>
     <t>DocumentReference.content.attachment.language</t>
   </si>
   <si>
@@ -1377,10 +1380,10 @@
     <t>langueDocument : [1..*] Code</t>
   </si>
   <si>
+    <t>DocumentEntry.languageCode</t>
+  </si>
+  <si>
     <t>./language</t>
-  </si>
-  <si>
-    <t>DocumentEntry.languageCode</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.data</t>
@@ -1444,13 +1447,13 @@
     <t>Document : [0..1]</t>
   </si>
   <si>
+    <t>DocumentEntry.repositoryUniqueId+DocumentEntry.uniqueId or DocumentEntry.URI</t>
+  </si>
+  <si>
     <t>./reference/literal</t>
   </si>
   <si>
     <t>RP.1+RP.2 - if they refer to a URL (see v2.6)</t>
-  </si>
-  <si>
-    <t>DocumentEntry.repositoryUniqueId or DocuemntEntry.URI</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.size</t>
@@ -1475,12 +1478,12 @@
     <t>Attachment.size</t>
   </si>
   <si>
+    <t>DocumentEntry.size</t>
+  </si>
+  <si>
     <t>N/A (needs data type R3 proposal)</t>
   </si>
   <si>
-    <t>DocumentEntry.size</t>
-  </si>
-  <si>
     <t>DocumentReference.content.attachment.hash</t>
   </si>
   <si>
@@ -1499,12 +1502,12 @@
     <t>Attachment.hash</t>
   </si>
   <si>
+    <t>DocumentEntry.hash</t>
+  </si>
+  <si>
     <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
   </si>
   <si>
-    <t>DocumentEntry.hash</t>
-  </si>
-  <si>
     <t>DocumentReference.content.attachment.title</t>
   </si>
   <si>
@@ -1526,10 +1529,10 @@
     <t>titreDocument : [0..1] Texte</t>
   </si>
   <si>
+    <t>DocumentEntry.title</t>
+  </si>
+  <si>
     <t>./title/data</t>
-  </si>
-  <si>
-    <t>DocumentEntry.title</t>
   </si>
   <si>
     <t>DocumentReference.content.attachment.creation</t>
@@ -1585,15 +1588,15 @@
     <t>formatDocument : [0..1] Code</t>
   </si>
   <si>
+    <t>DocumentEntry.formatCode</t>
+  </si>
+  <si>
     <t>Composition.meta.profile</t>
   </si>
   <si>
     <t>derived from the IHE Profile or Implementation Guide templateID</t>
   </si>
   <si>
-    <t>DocumentEntry.formatCode</t>
-  </si>
-  <si>
     <t>DocumentReference.context</t>
   </si>
   <si>
@@ -1621,7 +1624,7 @@
     <t>DocumentReference.context.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1631,6 +1634,9 @@
     <t>Describes the clinical encounter or type of care that the document content is associated with.</t>
   </si>
   <si>
+    <t>DocumentEntry.referenceIdList with CXi encoding for urn:ihe:iti:xds:2015:encounterId</t>
+  </si>
+  <si>
     <t>Event.context</t>
   </si>
   <si>
@@ -1641,9 +1647,6 @@
   </si>
   <si>
     <t>FiveWs.context</t>
-  </si>
-  <si>
-    <t>DocumentEntry.referenceIdList with CXi encoding for urn:ihe:iti:xds:2015:encounterId</t>
   </si>
   <si>
     <t>DocumentReference.context.event</t>
@@ -1671,13 +1674,13 @@
     <t>actePathologie : [0..1] Code</t>
   </si>
   <si>
+    <t>DocumentEntry.eventCodeList</t>
+  </si>
+  <si>
     <t>Composition.event.code</t>
   </si>
   <si>
     <t>.code</t>
-  </si>
-  <si>
-    <t>DocumentEntry.eventCodeList</t>
   </si>
   <si>
     <t>DocumentReference.context.period</t>
@@ -1737,15 +1740,15 @@
     <t>dateDebutActe : [0..1] DateHeure</t>
   </si>
   <si>
+    <t>DocumentEntry.serviceStartTime</t>
+  </si>
+  <si>
     <t>./low</t>
   </si>
   <si>
     <t>DR.1</t>
   </si>
   <si>
-    <t>DocumetEntry.serviceStartTime</t>
-  </si>
-  <si>
     <t>DocumentReference.context.period.end</t>
   </si>
   <si>
@@ -1767,13 +1770,13 @@
     <t>dateFinActe : [0..1] DateHeure</t>
   </si>
   <si>
+    <t>DocumentEntry.serviceStopTime</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
     <t>DR.2</t>
-  </si>
-  <si>
-    <t>DocumentEntry.serviceStopTime</t>
   </si>
   <si>
     <t>DocumentReference.context.facilityType</t>
@@ -1799,6 +1802,9 @@
     <t>secteurActivite : [0..1] Code</t>
   </si>
   <si>
+    <t>DocumentEntry.healthcareFacilityTypeCode</t>
+  </si>
+  <si>
     <t>usually from a mapping to a local ValueSet</t>
   </si>
   <si>
@@ -1806,9 +1812,6 @@
   </si>
   <si>
     <t>usually a mapping to a local ValueSet. Must be consistent with /clinicalDocument/code</t>
-  </si>
-  <si>
-    <t>DocumentEntry.healthcareFacilityTypeCode</t>
   </si>
   <si>
     <t>DocumentReference.context.practiceSetting</t>
@@ -1895,7 +1898,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1919,12 +1922,12 @@
     <t>Reference.identifier</t>
   </si>
   <si>
+    <t>DocumentEntry.sourcePatientId</t>
+  </si>
+  <si>
     <t>.identifier</t>
   </si>
   <si>
-    <t>DocumentEntry.sourcePatientId</t>
-  </si>
-  <si>
     <t>DocumentReference.context.sourcePatientInfo.display</t>
   </si>
   <si>
@@ -1943,7 +1946,7 @@
     <t>DocumentReference.context.related</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1963,6 +1966,9 @@
     <t>Slice based on the type.coding.system pattern</t>
   </si>
   <si>
+    <t>DocumentEntry.referenceIdList using CXi encoding for type when possible</t>
+  </si>
+  <si>
     <t>Composition.event.detail</t>
   </si>
   <si>
@@ -1975,9 +1981,6 @@
     <t>DocumentEntry.referenceIdList</t>
   </si>
   <si>
-    <t>DocumentEntry.referenceIdList using CXi encoding for type when possible</t>
-  </si>
-  <si>
     <t>DocumentReference.context.related:referenceIdList</t>
   </si>
   <si>
@@ -2009,9 +2012,6 @@
   </si>
   <si>
     <t>DocumentReference.context.related.type</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>DocumentReference.context.related:referenceIdList.identifier</t>
@@ -2382,10 +2382,6 @@
   </si>
   <si>
     <t>DocumentReference.context.related.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
   </si>
   <si>
     <t>Organization that issued id (may be just text)</t>
@@ -2765,14 +2761,14 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="77.77734375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="44.5859375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="68.71875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="44.5859375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="72.20703125" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="139.26953125" customWidth="true" bestFit="true"/>
-    <col min="45" max="45" width="68.71875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="72.20703125" customWidth="true" bestFit="true"/>
+    <col min="45" max="45" width="139.26953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3029,7 +3025,7 @@
         <v>94</v>
       </c>
       <c r="AP2" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>82</v>
@@ -3038,7 +3034,7 @@
         <v>82</v>
       </c>
       <c r="AS2" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" hidden="true">
@@ -3406,10 +3402,10 @@
         <v>82</v>
       </c>
       <c r="AN5" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO5" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO5" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP5" t="s" s="2">
         <v>82</v>
@@ -3535,10 +3531,10 @@
         <v>82</v>
       </c>
       <c r="AN6" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO6" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO6" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP6" t="s" s="2">
         <v>82</v>
@@ -4045,7 +4041,7 @@
         <v>82</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>82</v>
@@ -4066,7 +4062,7 @@
         <v>82</v>
       </c>
       <c r="AS10" t="s" s="2">
-        <v>151</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" hidden="true">
@@ -4696,10 +4692,10 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO15" t="s" s="2">
         <v>190</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
@@ -4825,10 +4821,10 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -5249,7 +5245,7 @@
         <v>82</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K20" t="s" s="2">
         <v>213</v>
@@ -5322,7 +5318,7 @@
         <v>97</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>109</v>
@@ -5331,36 +5327,36 @@
         <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="AP20" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AQ20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AR20" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AS20" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AS20" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5383,13 +5379,13 @@
         <v>98</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5428,7 +5424,7 @@
         <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
@@ -5438,7 +5434,7 @@
         <v>124</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>83</v>
@@ -5453,42 +5449,42 @@
         <v>109</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AS21" t="s" s="2">
         <v>232</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>82</v>
@@ -5501,22 +5497,22 @@
         <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5567,7 +5563,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>83</v>
@@ -5576,7 +5572,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>109</v>
@@ -5588,33 +5584,33 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>82</v>
+        <v>220</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>233</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>82</v>
+        <v>234</v>
       </c>
       <c r="AS22" t="s" s="2">
-        <v>82</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5640,13 +5636,13 @@
         <v>175</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5672,11 +5668,11 @@
         <v>82</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>82</v>
@@ -5694,7 +5690,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>97</v>
@@ -5712,36 +5708,36 @@
         <v>209</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="AN23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AR23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AS23" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="AS23" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5767,13 +5763,13 @@
         <v>175</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5799,13 +5795,13 @@
         <v>82</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>82</v>
@@ -5823,7 +5819,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5844,22 +5840,22 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>255</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>82</v>
@@ -5867,10 +5863,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5893,16 +5889,16 @@
         <v>98</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5932,7 +5928,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5950,7 +5946,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>83</v>
@@ -5962,46 +5958,46 @@
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -6020,16 +6016,16 @@
         <v>98</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -6059,7 +6055,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -6077,7 +6073,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>83</v>
@@ -6089,42 +6085,42 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>282</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>281</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AR26" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AS26" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6147,13 +6143,13 @@
         <v>98</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6204,7 +6200,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>83</v>
@@ -6219,43 +6215,43 @@
         <v>109</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AQ27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AR27" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AS27" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AQ27" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AR27" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AS27" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -6277,13 +6273,13 @@
         <v>134</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -6333,7 +6329,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -6351,7 +6347,7 @@
         <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>303</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>304</v>
@@ -6360,13 +6356,13 @@
         <v>305</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>306</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>306</v>
+        <v>82</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>82</v>
@@ -6377,10 +6373,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6403,16 +6399,16 @@
         <v>98</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6462,7 +6458,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>83</v>
@@ -6477,39 +6473,39 @@
         <v>109</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AN29" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AP29" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AQ29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR29" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AS29" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AP29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ29" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AR29" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AS29" t="s" s="2">
-        <v>318</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6532,16 +6528,16 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6591,7 +6587,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>83</v>
@@ -6606,39 +6602,39 @@
         <v>109</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="AN30" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AP30" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AQ30" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AR30" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AS30" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AQ30" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AS30" t="s" s="2">
-        <v>330</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6661,16 +6657,16 @@
         <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -6720,7 +6716,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6738,16 +6734,16 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>339</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -6759,15 +6755,15 @@
         <v>82</v>
       </c>
       <c r="AS31" t="s" s="2">
-        <v>338</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6790,16 +6786,16 @@
         <v>98</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6849,7 +6845,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6861,42 +6857,42 @@
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AP32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS32" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ32" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR32" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AS32" t="s" s="2">
-        <v>347</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7000,10 +6996,10 @@
         <v>82</v>
       </c>
       <c r="AN33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO33" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
@@ -7020,10 +7016,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7129,10 +7125,10 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -7149,14 +7145,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -7178,16 +7174,16 @@
         <v>118</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>121</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -7236,7 +7232,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -7260,10 +7256,10 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -7280,10 +7276,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7309,13 +7305,13 @@
         <v>175</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7341,13 +7337,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -7365,7 +7361,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>97</v>
@@ -7380,19 +7376,19 @@
         <v>109</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>366</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -7401,18 +7397,18 @@
         <v>82</v>
       </c>
       <c r="AR36" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="AS36" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7435,13 +7431,13 @@
         <v>98</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -7492,7 +7488,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>97</v>
@@ -7504,22 +7500,22 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>373</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -7528,18 +7524,18 @@
         <v>82</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AS37" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7565,16 +7561,16 @@
         <v>111</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7623,7 +7619,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7638,39 +7634,39 @@
         <v>109</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>383</v>
+        <v>82</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ38" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR38" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AS38" t="s" s="2">
         <v>384</v>
-      </c>
-      <c r="AR38" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AS38" t="s" s="2">
-        <v>385</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7693,19 +7689,19 @@
         <v>98</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7754,7 +7750,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7766,42 +7762,42 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="AP39" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AQ39" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR39" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AS39" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ39" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AR39" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AS39" t="s" s="2">
-        <v>397</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7824,13 +7820,13 @@
         <v>98</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7881,7 +7877,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>97</v>
@@ -7902,13 +7898,13 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>402</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -7925,10 +7921,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8032,10 +8028,10 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
@@ -8052,10 +8048,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8161,10 +8157,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -8181,14 +8177,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -8210,16 +8206,16 @@
         <v>118</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>121</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -8268,7 +8264,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -8292,10 +8288,10 @@
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO43" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -8312,10 +8308,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8338,13 +8334,13 @@
         <v>98</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -8395,7 +8391,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>97</v>
@@ -8416,33 +8412,33 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>413</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8546,10 +8542,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -8566,10 +8562,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8675,10 +8671,10 @@
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -8695,10 +8691,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8724,14 +8720,14 @@
         <v>175</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
@@ -8744,7 +8740,7 @@
         <v>82</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>82</v>
@@ -8756,13 +8752,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -8780,7 +8776,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8798,36 +8794,36 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>424</v>
+        <v>82</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>425</v>
+        <v>82</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8853,14 +8849,14 @@
         <v>175</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -8873,7 +8869,7 @@
         <v>82</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>82</v>
@@ -8909,7 +8905,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8924,19 +8920,19 @@
         <v>109</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8948,15 +8944,15 @@
         <v>82</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8979,19 +8975,19 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -9040,7 +9036,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -9064,19 +9060,19 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AR49" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AS49" t="s" s="2">
         <v>82</v>
@@ -9084,10 +9080,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9110,19 +9106,19 @@
         <v>98</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -9135,7 +9131,7 @@
         <v>82</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>82</v>
@@ -9171,7 +9167,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -9183,42 +9179,42 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>455</v>
+        <v>82</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9241,19 +9237,19 @@
         <v>98</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -9302,7 +9298,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9320,16 +9316,16 @@
         <v>82</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -9341,15 +9337,15 @@
         <v>82</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9372,19 +9368,19 @@
         <v>98</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -9433,7 +9429,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9451,16 +9447,16 @@
         <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -9472,15 +9468,15 @@
         <v>82</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>474</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9506,14 +9502,14 @@
         <v>111</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -9526,7 +9522,7 @@
         <v>82</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>82</v>
@@ -9562,7 +9558,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9577,19 +9573,19 @@
         <v>109</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>82</v>
+        <v>483</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>484</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -9601,15 +9597,15 @@
         <v>82</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9632,17 +9628,17 @@
         <v>98</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -9691,7 +9687,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9706,19 +9702,19 @@
         <v>109</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9730,15 +9726,15 @@
         <v>82</v>
       </c>
       <c r="AS54" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9764,13 +9760,13 @@
         <v>153</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9800,7 +9796,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -9818,7 +9814,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9830,42 +9826,42 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>402</v>
+        <v>501</v>
       </c>
       <c r="AO55" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AP55" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR55" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS55" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AP55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR55" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AS55" t="s" s="2">
-        <v>501</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9888,16 +9884,16 @@
         <v>98</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9947,7 +9943,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9971,10 +9967,10 @@
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>82</v>
+        <v>507</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9991,10 +9987,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10098,10 +10094,10 @@
         <v>82</v>
       </c>
       <c r="AN57" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -10118,10 +10114,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10227,10 +10223,10 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO58" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -10247,14 +10243,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -10276,16 +10272,16 @@
         <v>118</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>121</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -10334,7 +10330,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -10358,10 +10354,10 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO59" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -10378,10 +10374,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10404,13 +10400,13 @@
         <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10461,7 +10457,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10479,36 +10475,36 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>82</v>
+        <v>518</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AS60" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10531,16 +10527,16 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10569,10 +10565,10 @@
         <v>165</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -10590,7 +10586,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10602,42 +10598,42 @@
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>527</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AP61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS61" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR61" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AS61" t="s" s="2">
-        <v>529</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10660,13 +10656,13 @@
         <v>98</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10717,7 +10713,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10738,7 +10734,7 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>535</v>
@@ -10747,24 +10743,24 @@
         <v>536</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>82</v>
+        <v>537</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>537</v>
+        <v>82</v>
       </c>
       <c r="AS62" t="s" s="2">
-        <v>82</v>
+        <v>538</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10868,10 +10864,10 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO63" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
@@ -10888,10 +10884,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10997,10 +10993,10 @@
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>82</v>
@@ -11017,10 +11013,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11043,16 +11039,16 @@
         <v>98</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -11102,7 +11098,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -11111,45 +11107,45 @@
         <v>97</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="AR65" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="AS65" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11172,23 +11168,23 @@
         <v>98</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="R66" t="s" s="2">
         <v>82</v>
@@ -11233,7 +11229,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -11242,45 +11238,45 @@
         <v>97</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>557</v>
+        <v>82</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>82</v>
+        <v>559</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>82</v>
+        <v>560</v>
       </c>
       <c r="AS66" t="s" s="2">
-        <v>559</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11303,13 +11299,13 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11340,7 +11336,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -11358,7 +11354,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11370,42 +11366,42 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>567</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
       <c r="AN67" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AQ67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR67" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AS67" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AR67" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AS67" t="s" s="2">
-        <v>569</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11428,19 +11424,19 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -11469,7 +11465,7 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -11487,7 +11483,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11499,42 +11495,42 @@
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AS68" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11557,13 +11553,13 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -11614,7 +11610,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11635,33 +11631,33 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>582</v>
+        <v>82</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>82</v>
+        <v>583</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11765,10 +11761,10 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>82</v>
@@ -11785,10 +11781,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11894,10 +11890,10 @@
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO71" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>82</v>
@@ -11914,10 +11910,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11943,13 +11939,13 @@
         <v>111</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11999,7 +11995,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -12008,7 +12004,7 @@
         <v>97</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>109</v>
@@ -12017,17 +12013,17 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>82</v>
+        <v>592</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO72" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AO72" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP72" t="s" s="2">
         <v>82</v>
       </c>
@@ -12038,15 +12034,15 @@
         <v>82</v>
       </c>
       <c r="AS72" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12072,13 +12068,13 @@
         <v>140</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -12107,10 +12103,10 @@
         <v>157</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>82</v>
@@ -12128,7 +12124,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -12152,10 +12148,10 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO73" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>82</v>
@@ -12172,10 +12168,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12198,16 +12194,16 @@
         <v>98</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12257,7 +12253,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12275,16 +12271,16 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>605</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>82</v>
@@ -12296,15 +12292,15 @@
         <v>82</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>605</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12330,13 +12326,13 @@
         <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -12386,7 +12382,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12410,10 +12406,10 @@
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO75" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>82</v>
@@ -12430,10 +12426,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12456,16 +12452,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12503,10 +12499,10 @@
         <v>82</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>82</v>
@@ -12515,7 +12511,7 @@
         <v>124</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12533,39 +12529,39 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>82</v>
@@ -12587,16 +12583,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12646,7 +12642,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12664,36 +12660,36 @@
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>82</v>
+        <v>619</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>618</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="AS77" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12797,10 +12793,10 @@
         <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO78" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO78" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>82</v>
@@ -12817,10 +12813,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12926,10 +12922,10 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO79" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO79" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>82</v>
@@ -12946,10 +12942,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12975,13 +12971,13 @@
         <v>111</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -13031,7 +13027,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -13040,7 +13036,7 @@
         <v>97</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>109</v>
@@ -13055,10 +13051,10 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>82</v>
@@ -13075,10 +13071,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13104,13 +13100,13 @@
         <v>140</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13139,10 +13135,10 @@
         <v>157</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>634</v>
+        <v>598</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -13160,7 +13156,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -13184,10 +13180,10 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO81" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO81" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>82</v>
@@ -13230,16 +13226,16 @@
         <v>98</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -13289,7 +13285,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13313,10 +13309,10 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>604</v>
+        <v>82</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>82</v>
@@ -13440,10 +13436,10 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO83" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>82</v>
@@ -13569,10 +13565,10 @@
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO84" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>82</v>
@@ -13652,7 +13648,7 @@
         <v>82</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Y85" t="s" s="2">
         <v>647</v>
@@ -13700,19 +13696,19 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO85" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AO85" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ85" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR85" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AR85" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS85" t="s" s="2">
         <v>82</v>
@@ -13746,7 +13742,7 @@
         <v>98</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L86" t="s" s="2">
         <v>653</v>
@@ -13831,19 +13827,19 @@
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="AO86" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR86" t="s" s="2">
         <v>660</v>
-      </c>
-      <c r="AR86" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS86" t="s" s="2">
         <v>82</v>
@@ -13958,10 +13954,10 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO87" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>82</v>
@@ -14087,10 +14083,10 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO88" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>82</v>
@@ -14218,19 +14214,19 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO89" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="AO89" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ89" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR89" t="s" s="2">
         <v>673</v>
-      </c>
-      <c r="AR89" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS89" t="s" s="2">
         <v>82</v>
@@ -14345,10 +14341,10 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO90" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>82</v>
@@ -14474,10 +14470,10 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO91" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>82</v>
@@ -14605,19 +14601,19 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO92" t="s" s="2">
         <v>686</v>
       </c>
-      <c r="AO92" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ92" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR92" t="s" s="2">
         <v>687</v>
-      </c>
-      <c r="AR92" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS92" t="s" s="2">
         <v>82</v>
@@ -14734,19 +14730,19 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO93" t="s" s="2">
         <v>694</v>
       </c>
-      <c r="AO93" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ93" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR93" t="s" s="2">
         <v>695</v>
-      </c>
-      <c r="AR93" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS93" t="s" s="2">
         <v>82</v>
@@ -14863,19 +14859,19 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR94" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="AR94" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS94" t="s" s="2">
         <v>82</v>
@@ -14992,19 +14988,19 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO95" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR95" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS95" t="s" s="2">
         <v>82</v>
@@ -15123,19 +15119,19 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR96" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="AR96" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS96" t="s" s="2">
         <v>82</v>
@@ -15254,19 +15250,19 @@
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO97" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="AO97" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR97" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS97" t="s" s="2">
         <v>82</v>
@@ -15385,19 +15381,19 @@
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO98" t="s" s="2">
         <v>738</v>
       </c>
-      <c r="AO98" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ98" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR98" t="s" s="2">
         <v>739</v>
-      </c>
-      <c r="AR98" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS98" t="s" s="2">
         <v>82</v>
@@ -15514,19 +15510,19 @@
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO99" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="AO99" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR99" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="AR99" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS99" t="s" s="2">
         <v>82</v>
@@ -15560,7 +15556,7 @@
         <v>98</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>751</v>
@@ -15641,19 +15637,19 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO100" t="s" s="2">
         <v>754</v>
       </c>
-      <c r="AO100" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AP100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AQ100" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR100" t="s" s="2">
         <v>755</v>
-      </c>
-      <c r="AR100" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS100" t="s" s="2">
         <v>82</v>
@@ -15687,16 +15683,16 @@
         <v>98</v>
       </c>
       <c r="K101" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="L101" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="L101" t="s" s="2">
+      <c r="M101" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -15746,7 +15742,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>83</v>
@@ -15770,19 +15766,19 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AQ101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AR101" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AQ101" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="AR101" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AS101" t="s" s="2">
         <v>82</v>
@@ -15790,10 +15786,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>765</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>766</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15819,13 +15815,13 @@
         <v>111</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -15875,7 +15871,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>83</v>
@@ -15899,10 +15895,10 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO102" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>82</v>
